--- a/data/Parametros.xlsx
+++ b/data/Parametros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1510d6d17ff2404d/99-DESARROLLO/Python/DataSmartExpress/App_DataSmart_Express/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="491" documentId="11_076110159C8BD21570149374E46859E1E1308BCD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F806B7BE-5BA5-477D-AD0C-964F3697CAD0}"/>
+  <xr:revisionPtr revIDLastSave="547" documentId="11_076110159C8BD21570149374E46859E1E1308BCD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C800B12-055A-4FF8-A6C3-C155C4AE9FB4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KPIS_FINANCIEROS" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="81">
   <si>
     <t>GRUPO</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>GRAFICAS_INTELIGENTES</t>
+  </si>
+  <si>
+    <t>Premium_trial</t>
   </si>
 </sst>
 </file>
@@ -322,7 +325,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -356,11 +359,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -394,6 +406,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -698,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
@@ -708,7 +729,7 @@
     <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -736,8 +757,11 @@
       <c r="I1" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -765,8 +789,11 @@
       <c r="I2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -794,8 +821,11 @@
       <c r="I3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -823,8 +853,11 @@
       <c r="I4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -852,8 +885,11 @@
       <c r="I5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -881,8 +917,11 @@
       <c r="I6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -910,8 +949,11 @@
       <c r="I7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -939,8 +981,11 @@
       <c r="I8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -968,8 +1013,11 @@
       <c r="I9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -995,6 +1043,9 @@
         <v>1</v>
       </c>
       <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
         <v>1</v>
       </c>
     </row>
@@ -1005,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1A63FD-C732-483A-BB65-70FBDDBA7676}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1020,7 +1071,7 @@
     <col min="11" max="11" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
@@ -1057,8 +1108,11 @@
       <c r="L1" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1092,8 +1146,11 @@
       <c r="L2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1130,8 +1187,11 @@
       <c r="L3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1165,8 +1225,11 @@
       <c r="L4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1200,8 +1263,11 @@
       <c r="L5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1233,6 +1299,9 @@
         <v>1</v>
       </c>
       <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -1243,13 +1312,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E68DE59-992B-4058-A203-82C1DEABD0B6}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>77</v>
       </c>
@@ -1265,8 +1334,11 @@
       <c r="E1" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -1282,8 +1354,11 @@
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -1297,6 +1372,9 @@
         <v>0</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
     </row>
@@ -1307,13 +1385,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC8F708E-264A-4BE0-B59B-C2CBA66A93D2}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="31.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
@@ -1338,8 +1416,11 @@
       <c r="H1" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1364,8 +1445,11 @@
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1390,8 +1474,11 @@
       <c r="H3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1416,8 +1503,11 @@
       <c r="H4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1442,8 +1532,11 @@
       <c r="H5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1468,8 +1561,11 @@
       <c r="H6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1494,8 +1590,11 @@
       <c r="H7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1520,8 +1619,11 @@
       <c r="H8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1546,8 +1648,11 @@
       <c r="H9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1572,8 +1677,11 @@
       <c r="H10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1598,8 +1706,11 @@
       <c r="H11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1624,8 +1735,11 @@
       <c r="H12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1648,6 +1762,9 @@
         <v>1</v>
       </c>
       <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
         <v>1</v>
       </c>
     </row>
@@ -1659,13 +1776,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7CFF8A-3790-4A69-BD86-157F17280CF7}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>68</v>
       </c>
@@ -1681,8 +1798,11 @@
       <c r="E1" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F1" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>69</v>
       </c>
@@ -1698,8 +1818,11 @@
       <c r="E2" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F2" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>70</v>
       </c>
@@ -1715,8 +1838,11 @@
       <c r="E3" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F3" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>71</v>
       </c>
@@ -1732,8 +1858,11 @@
       <c r="E4" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F4" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>72</v>
       </c>
@@ -1749,8 +1878,11 @@
       <c r="E5" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>73</v>
       </c>
@@ -1766,8 +1898,11 @@
       <c r="E6" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>74</v>
       </c>
@@ -1783,8 +1918,11 @@
       <c r="E7" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F7" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>75</v>
       </c>
@@ -1798,6 +1936,9 @@
         <v>0</v>
       </c>
       <c r="E8" s="11">
+        <v>1</v>
+      </c>
+      <c r="F8" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1808,7 +1949,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD2B396-A028-439B-AD56-80C88A7629A9}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" style="12" customWidth="1"/>
@@ -1816,9 +1957,10 @@
     <col min="3" max="3" width="19.77734375" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>38</v>
       </c>
@@ -1834,8 +1976,11 @@
       <c r="E1" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>44</v>
       </c>
@@ -1851,8 +1996,11 @@
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>35</v>
       </c>
@@ -1868,8 +2016,11 @@
       <c r="E3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>36</v>
       </c>
@@ -1885,8 +2036,11 @@
       <c r="E4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>37</v>
       </c>
@@ -1902,8 +2056,11 @@
       <c r="E5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>34</v>
       </c>
@@ -1919,8 +2076,11 @@
       <c r="E6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>39</v>
       </c>
@@ -1936,8 +2096,11 @@
       <c r="E7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>45</v>
       </c>
@@ -1953,8 +2116,11 @@
       <c r="E8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>57</v>
       </c>
@@ -1970,8 +2136,11 @@
       <c r="E9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>79</v>
       </c>
@@ -1985,6 +2154,9 @@
         <v>0</v>
       </c>
       <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
     </row>
